--- a/SeleniumTests/TestDataFolder/BatchProcessTestDataValid.xlsx
+++ b/SeleniumTests/TestDataFolder/BatchProcessTestDataValid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274A53BE-25A3-4FD4-BAF4-67A638A5A9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F24168-80A5-4BEF-997B-00EC6DA2F2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38700" yWindow="3525" windowWidth="18405" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExportBatchReportTestData" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>rowNumber</t>
+    <t>File Row No. (Digit)</t>
   </si>
 </sst>
 </file>
@@ -361,7 +361,7 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.44140625" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
